--- a/Excel/Datas/card_item.xlsx
+++ b/Excel/Datas/card_item.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="30240" windowHeight="12920"/>
+    <workbookView windowWidth="28000" windowHeight="12920"/>
   </bookViews>
   <sheets>
     <sheet name="card_item_table" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="7">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="12">
   <si>
     <t>##var</t>
   </si>
@@ -35,10 +35,16 @@
     <t>id</t>
   </si>
   <si>
+    <t>type</t>
+  </si>
+  <si>
     <t>##type</t>
   </si>
   <si>
     <t>ItemEnum</t>
+  </si>
+  <si>
+    <t>CardTypeEnum</t>
   </si>
   <si>
     <t>##group</t>
@@ -48,6 +54,15 @@
   </si>
   <si>
     <t>ID</t>
+  </si>
+  <si>
+    <t>牌的类型</t>
+  </si>
+  <si>
+    <t>回血0</t>
+  </si>
+  <si>
+    <t>道具卡</t>
   </si>
 </sst>
 </file>
@@ -1086,7 +1101,9 @@
       <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1"/>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
       <c r="D1" s="1"/>
       <c r="E1" s="1"/>
       <c r="F1" s="1"/>
@@ -1109,12 +1126,14 @@
     </row>
     <row r="3" spans="1:9">
       <c r="A3" s="1" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
-      <c r="C3" s="1"/>
+      <c r="C3" s="1" t="s">
+        <v>5</v>
+      </c>
       <c r="D3" s="1"/>
       <c r="E3" s="1"/>
       <c r="F3" s="1"/>
@@ -1124,7 +1143,7 @@
     </row>
     <row r="4" spans="1:9">
       <c r="A4" s="1" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="B4" s="1"/>
       <c r="C4" s="1"/>
@@ -1137,12 +1156,14 @@
     </row>
     <row r="5" ht="17.55" spans="1:9">
       <c r="A5" s="2" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
-      <c r="C5" s="2"/>
+      <c r="C5" s="2" t="s">
+        <v>9</v>
+      </c>
       <c r="D5" s="2"/>
       <c r="E5" s="2"/>
       <c r="F5" s="7"/>
@@ -1150,9 +1171,13 @@
       <c r="H5" s="8"/>
       <c r="I5" s="8"/>
     </row>
-    <row r="6" ht="17.55" spans="2:9">
-      <c r="B6" s="3"/>
-      <c r="C6" s="3"/>
+    <row r="6" spans="2:9">
+      <c r="B6" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>11</v>
+      </c>
       <c r="D6" s="4"/>
       <c r="E6" s="4"/>
       <c r="F6" s="9"/>

--- a/Excel/Datas/card_item.xlsx
+++ b/Excel/Datas/card_item.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28000" windowHeight="12920"/>
+    <workbookView windowWidth="23040" windowHeight="10620"/>
   </bookViews>
   <sheets>
     <sheet name="card_item_table" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="28">
   <si>
     <t>##var</t>
   </si>
@@ -35,6 +35,12 @@
     <t>id</t>
   </si>
   <si>
+    <t>name</t>
+  </si>
+  <si>
+    <t>description</t>
+  </si>
+  <si>
     <t>type</t>
   </si>
   <si>
@@ -44,6 +50,9 @@
     <t>ItemEnum</t>
   </si>
   <si>
+    <t>string</t>
+  </si>
+  <si>
     <t>CardTypeEnum</t>
   </si>
   <si>
@@ -56,13 +65,52 @@
     <t>ID</t>
   </si>
   <si>
-    <t>牌的类型</t>
-  </si>
-  <si>
-    <t>回血0</t>
-  </si>
-  <si>
-    <t>道具卡</t>
+    <t>SpeedUpgrade</t>
+  </si>
+  <si>
+    <t>高速升级</t>
+  </si>
+  <si>
+    <t>对目标己方怪兽使用。本次对战中，该怪兽的速度提高10点。如果该怪兽的种族是机械，则改为该怪兽的速度永久提高2点。</t>
+  </si>
+  <si>
+    <t>Stuff</t>
+  </si>
+  <si>
+    <t>ArmorUpgrade</t>
+  </si>
+  <si>
+    <t>装甲升级</t>
+  </si>
+  <si>
+    <t>对目标己方怪兽使用。本次对战中，该怪兽的力量和防御分别提高10点。如果该怪兽的种族是机械，则改为该怪兽的力量和防御分别永久提高1点。</t>
+  </si>
+  <si>
+    <t>RebirthUpgrade</t>
+  </si>
+  <si>
+    <t>重组升级</t>
+  </si>
+  <si>
+    <t>对目标己方怪兽使用。本次对战中，该怪兽的恢复最大生命的50%。如果该怪兽的种族是机械，则改为该怪兽的最大生命永久提高5点。</t>
+  </si>
+  <si>
+    <t>EnergyDrink</t>
+  </si>
+  <si>
+    <t>33能量饮料</t>
+  </si>
+  <si>
+    <t>对目标怪兽使用。如果目标是己方怪兽，则该怪兽接下来3次攻击会造成3倍伤害；如果目标是敌方怪兽，则该怪兽的力量降低80%。</t>
+  </si>
+  <si>
+    <t>DirtyMop</t>
+  </si>
+  <si>
+    <t>脏拖把</t>
+  </si>
+  <si>
+    <t>对目标敌方单位使用。该单位受到30点伤害（此伤害无视防御和适应）。</t>
   </si>
 </sst>
 </file>
@@ -75,7 +123,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="21">
+  <fonts count="22">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -86,6 +134,13 @@
     <font>
       <sz val="10"/>
       <color theme="1"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
       <name val="等线"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -235,7 +290,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="35">
+  <fills count="36">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -256,6 +311,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFFFFFCC"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -441,7 +502,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="12">
+  <borders count="13">
     <border>
       <left/>
       <right/>
@@ -461,6 +522,21 @@
       </top>
       <bottom style="thin">
         <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFDEE0E3"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFDEE0E3"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFDEE0E3"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFDEE0E3"/>
       </bottom>
       <diagonal/>
     </border>
@@ -608,55 +684,52 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="6" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="6" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="7" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="7" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="8" borderId="10" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="12" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -671,95 +744,101 @@
     <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -1087,10 +1166,10 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:I20"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8"/>
   <cols>
     <col min="2" max="2" width="18.5" customWidth="1"/>
-    <col min="3" max="5" width="21.625" customWidth="1"/>
+    <col min="3" max="5" width="21.6296296296296" customWidth="1"/>
     <col min="6" max="9" width="13.5" customWidth="1"/>
   </cols>
   <sheetData>
@@ -1104,12 +1183,16 @@
       <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1"/>
-      <c r="E1" s="1"/>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
       <c r="F1" s="1"/>
       <c r="G1" s="1"/>
-      <c r="H1" s="6"/>
-      <c r="I1" s="6"/>
+      <c r="H1" s="2"/>
+      <c r="I1" s="2"/>
     </row>
     <row r="2" spans="1:9">
       <c r="A2" s="1" t="s">
@@ -1126,24 +1209,28 @@
     </row>
     <row r="3" spans="1:9">
       <c r="A3" s="1" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="D3" s="1"/>
-      <c r="E3" s="1"/>
+        <v>7</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>8</v>
+      </c>
       <c r="F3" s="1"/>
       <c r="G3" s="1"/>
-      <c r="H3" s="6"/>
-      <c r="I3" s="6"/>
+      <c r="H3" s="2"/>
+      <c r="I3" s="2"/>
     </row>
     <row r="4" spans="1:9">
       <c r="A4" s="1" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="B4" s="1"/>
       <c r="C4" s="1"/>
@@ -1154,155 +1241,189 @@
       <c r="H4" s="1"/>
       <c r="I4" s="1"/>
     </row>
-    <row r="5" ht="17.55" spans="1:9">
-      <c r="A5" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D5" s="2"/>
-      <c r="E5" s="2"/>
-      <c r="F5" s="7"/>
-      <c r="G5" s="7"/>
-      <c r="H5" s="8"/>
-      <c r="I5" s="8"/>
-    </row>
-    <row r="6" spans="2:9">
-      <c r="B6" s="3" t="s">
+    <row r="5" spans="1:9">
+      <c r="A5" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C6" s="3" t="s">
+      <c r="B5" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="D6" s="4"/>
-      <c r="E6" s="4"/>
-      <c r="F6" s="9"/>
-      <c r="G6" s="9"/>
-      <c r="H6" s="9"/>
-      <c r="I6" s="9"/>
-    </row>
-    <row r="7" ht="17.55" spans="2:9">
-      <c r="B7" s="4"/>
-      <c r="C7" s="4"/>
-      <c r="D7" s="4"/>
-      <c r="E7" s="4"/>
-      <c r="F7" s="9"/>
-      <c r="G7" s="9"/>
-      <c r="H7" s="9"/>
-      <c r="I7" s="9"/>
-    </row>
-    <row r="8" ht="17.55" spans="2:9">
-      <c r="B8" s="4"/>
-      <c r="C8" s="4"/>
-      <c r="D8" s="4"/>
-      <c r="E8" s="4"/>
-      <c r="F8" s="5"/>
-      <c r="G8" s="5"/>
-      <c r="H8" s="5"/>
-      <c r="I8" s="5"/>
-    </row>
-    <row r="9" ht="17.55" spans="2:9">
-      <c r="B9" s="4"/>
-      <c r="C9" s="4"/>
-      <c r="D9" s="4"/>
-      <c r="E9" s="4"/>
-      <c r="F9" s="5"/>
-      <c r="G9" s="5"/>
-      <c r="H9" s="5"/>
-      <c r="I9" s="5"/>
-    </row>
-    <row r="10" ht="17.55" spans="2:9">
-      <c r="B10" s="4"/>
-      <c r="C10" s="4"/>
-      <c r="D10" s="4"/>
-      <c r="E10" s="4"/>
-      <c r="F10" s="5"/>
-      <c r="G10" s="5"/>
-      <c r="H10" s="5"/>
-      <c r="I10" s="5"/>
-    </row>
-    <row r="11" ht="17.55" spans="2:9">
-      <c r="B11" s="4"/>
-      <c r="C11" s="4"/>
-      <c r="D11" s="4"/>
-      <c r="E11" s="4"/>
-      <c r="F11" s="5"/>
-      <c r="G11" s="5"/>
-      <c r="H11" s="5"/>
-      <c r="I11" s="5"/>
-    </row>
-    <row r="12" ht="17.55" spans="2:9">
-      <c r="B12" s="4"/>
-      <c r="C12" s="4"/>
-      <c r="D12" s="4"/>
-      <c r="E12" s="4"/>
-      <c r="F12" s="5"/>
-      <c r="G12" s="5"/>
-      <c r="H12" s="5"/>
-      <c r="I12" s="5"/>
-    </row>
-    <row r="13" ht="17.55" spans="2:9">
-      <c r="B13" s="4"/>
-      <c r="C13" s="4"/>
-      <c r="D13" s="4"/>
-      <c r="E13" s="4"/>
-      <c r="F13" s="5"/>
-      <c r="G13" s="5"/>
-      <c r="H13" s="5"/>
-      <c r="I13" s="5"/>
-    </row>
-    <row r="14" ht="17.55" spans="2:9">
-      <c r="B14" s="4"/>
-      <c r="C14" s="4"/>
-      <c r="D14" s="4"/>
-      <c r="E14" s="4"/>
-      <c r="F14" s="5"/>
-      <c r="G14" s="5"/>
-      <c r="H14" s="5"/>
-      <c r="I14" s="5"/>
-    </row>
-    <row r="15" ht="17.55" spans="2:9">
-      <c r="B15" s="4"/>
-      <c r="C15" s="4"/>
-      <c r="D15" s="4"/>
-      <c r="E15" s="4"/>
-      <c r="F15" s="5"/>
-      <c r="G15" s="5"/>
-      <c r="H15" s="5"/>
-      <c r="I15" s="5"/>
-    </row>
-    <row r="16" ht="17.55" spans="2:9">
-      <c r="B16" s="4"/>
-      <c r="C16" s="4"/>
-      <c r="D16" s="4"/>
-      <c r="E16" s="4"/>
-      <c r="F16" s="5"/>
-      <c r="G16" s="5"/>
-      <c r="H16" s="5"/>
-      <c r="I16" s="5"/>
-    </row>
-    <row r="17" ht="17.55" spans="2:9">
-      <c r="B17" s="4"/>
-      <c r="C17" s="4"/>
-      <c r="D17" s="4"/>
-      <c r="E17" s="4"/>
-      <c r="F17" s="5"/>
-      <c r="G17" s="5"/>
-      <c r="H17" s="5"/>
-      <c r="I17" s="5"/>
-    </row>
-    <row r="18" ht="17.55" spans="2:2">
-      <c r="B18" s="5"/>
-    </row>
-    <row r="19" ht="17.55" spans="2:2">
-      <c r="B19" s="5"/>
-    </row>
-    <row r="20" ht="17.55" spans="2:2">
-      <c r="B20" s="5"/>
+      <c r="C5" s="3"/>
+      <c r="D5" s="3"/>
+      <c r="E5" s="3"/>
+      <c r="F5" s="4"/>
+      <c r="G5" s="4"/>
+      <c r="H5" s="5"/>
+      <c r="I5" s="5"/>
+    </row>
+    <row r="6" ht="14.55" spans="2:9">
+      <c r="B6" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="C6" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="D6" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="E6" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="F6" s="8"/>
+      <c r="G6" s="8"/>
+      <c r="H6" s="8"/>
+      <c r="I6" s="8"/>
+    </row>
+    <row r="7" ht="14.55" spans="2:9">
+      <c r="B7" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="C7" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="D7" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="E7" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="F7" s="8"/>
+      <c r="G7" s="8"/>
+      <c r="H7" s="8"/>
+      <c r="I7" s="8"/>
+    </row>
+    <row r="8" ht="14.55" spans="2:9">
+      <c r="B8" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="C8" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="D8" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="E8" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="F8" s="9"/>
+      <c r="G8" s="9"/>
+      <c r="H8" s="9"/>
+      <c r="I8" s="9"/>
+    </row>
+    <row r="9" ht="14.55" spans="2:9">
+      <c r="B9" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="C9" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="D9" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="E9" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="F9" s="9"/>
+      <c r="G9" s="9"/>
+      <c r="H9" s="9"/>
+      <c r="I9" s="9"/>
+    </row>
+    <row r="10" ht="14.55" spans="2:9">
+      <c r="B10" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="C10" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="D10" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="E10" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="F10" s="9"/>
+      <c r="G10" s="9"/>
+      <c r="H10" s="9"/>
+      <c r="I10" s="9"/>
+    </row>
+    <row r="11" ht="14.55" spans="2:9">
+      <c r="B11" s="10"/>
+      <c r="C11" s="10"/>
+      <c r="D11" s="10"/>
+      <c r="E11" s="10"/>
+      <c r="F11" s="9"/>
+      <c r="G11" s="9"/>
+      <c r="H11" s="9"/>
+      <c r="I11" s="9"/>
+    </row>
+    <row r="12" ht="14.55" spans="2:9">
+      <c r="B12" s="10"/>
+      <c r="C12" s="10"/>
+      <c r="D12" s="10"/>
+      <c r="E12" s="10"/>
+      <c r="F12" s="9"/>
+      <c r="G12" s="9"/>
+      <c r="H12" s="9"/>
+      <c r="I12" s="9"/>
+    </row>
+    <row r="13" ht="14.55" spans="2:9">
+      <c r="B13" s="10"/>
+      <c r="C13" s="10"/>
+      <c r="D13" s="10"/>
+      <c r="E13" s="10"/>
+      <c r="F13" s="9"/>
+      <c r="G13" s="9"/>
+      <c r="H13" s="9"/>
+      <c r="I13" s="9"/>
+    </row>
+    <row r="14" ht="14.55" spans="2:9">
+      <c r="B14" s="10"/>
+      <c r="C14" s="10"/>
+      <c r="D14" s="10"/>
+      <c r="E14" s="10"/>
+      <c r="F14" s="9"/>
+      <c r="G14" s="9"/>
+      <c r="H14" s="9"/>
+      <c r="I14" s="9"/>
+    </row>
+    <row r="15" ht="14.55" spans="2:9">
+      <c r="B15" s="10"/>
+      <c r="C15" s="10"/>
+      <c r="D15" s="10"/>
+      <c r="E15" s="10"/>
+      <c r="F15" s="9"/>
+      <c r="G15" s="9"/>
+      <c r="H15" s="9"/>
+      <c r="I15" s="9"/>
+    </row>
+    <row r="16" ht="14.55" spans="2:9">
+      <c r="B16" s="10"/>
+      <c r="C16" s="10"/>
+      <c r="D16" s="10"/>
+      <c r="E16" s="10"/>
+      <c r="F16" s="9"/>
+      <c r="G16" s="9"/>
+      <c r="H16" s="9"/>
+      <c r="I16" s="9"/>
+    </row>
+    <row r="17" ht="14.55" spans="2:9">
+      <c r="B17" s="10"/>
+      <c r="C17" s="10"/>
+      <c r="D17" s="10"/>
+      <c r="E17" s="10"/>
+      <c r="F17" s="9"/>
+      <c r="G17" s="9"/>
+      <c r="H17" s="9"/>
+      <c r="I17" s="9"/>
+    </row>
+    <row r="18" ht="14.55" spans="2:2">
+      <c r="B18" s="9"/>
+    </row>
+    <row r="19" ht="14.55" spans="2:2">
+      <c r="B19" s="9"/>
+    </row>
+    <row r="20" ht="14.55" spans="2:2">
+      <c r="B20" s="9"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Excel/Datas/card_item.xlsx
+++ b/Excel/Datas/card_item.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="23040" windowHeight="10620"/>
+    <workbookView windowWidth="28000" windowHeight="12920"/>
   </bookViews>
   <sheets>
     <sheet name="card_item_table" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="24">
   <si>
     <t>##var</t>
   </si>
@@ -65,19 +65,13 @@
     <t>ID</t>
   </si>
   <si>
-    <t>SpeedUpgrade</t>
-  </si>
-  <si>
     <t>高速升级</t>
   </si>
   <si>
     <t>对目标己方怪兽使用。本次对战中，该怪兽的速度提高10点。如果该怪兽的种族是机械，则改为该怪兽的速度永久提高2点。</t>
   </si>
   <si>
-    <t>Stuff</t>
-  </si>
-  <si>
-    <t>ArmorUpgrade</t>
+    <t>道具卡</t>
   </si>
   <si>
     <t>装甲升级</t>
@@ -86,25 +80,19 @@
     <t>对目标己方怪兽使用。本次对战中，该怪兽的力量和防御分别提高10点。如果该怪兽的种族是机械，则改为该怪兽的力量和防御分别永久提高1点。</t>
   </si>
   <si>
-    <t>RebirthUpgrade</t>
-  </si>
-  <si>
     <t>重组升级</t>
   </si>
   <si>
     <t>对目标己方怪兽使用。本次对战中，该怪兽的恢复最大生命的50%。如果该怪兽的种族是机械，则改为该怪兽的最大生命永久提高5点。</t>
   </si>
   <si>
-    <t>EnergyDrink</t>
+    <t>能量饮料</t>
   </si>
   <si>
     <t>33能量饮料</t>
   </si>
   <si>
     <t>对目标怪兽使用。如果目标是己方怪兽，则该怪兽接下来3次攻击会造成3倍伤害；如果目标是敌方怪兽，则该怪兽的力量降低80%。</t>
-  </si>
-  <si>
-    <t>DirtyMop</t>
   </si>
   <si>
     <t>脏拖把</t>
@@ -133,14 +121,14 @@
     </font>
     <font>
       <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
       <color theme="1"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color rgb="FF000000"/>
       <name val="等线"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -547,7 +535,9 @@
       <right style="medium">
         <color rgb="FFDEE0E3"/>
       </right>
-      <top/>
+      <top style="medium">
+        <color rgb="FFDEE0E3"/>
+      </top>
       <bottom style="medium">
         <color rgb="FFDEE0E3"/>
       </bottom>
@@ -560,9 +550,7 @@
       <right style="medium">
         <color rgb="FFDEE0E3"/>
       </right>
-      <top style="medium">
-        <color rgb="FFDEE0E3"/>
-      </top>
+      <top/>
       <bottom style="medium">
         <color rgb="FFDEE0E3"/>
       </bottom>
@@ -817,28 +805,28 @@
   <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -1166,10 +1154,10 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:I20"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8"/>
   <cols>
     <col min="2" max="2" width="18.5" customWidth="1"/>
-    <col min="3" max="5" width="21.6296296296296" customWidth="1"/>
+    <col min="3" max="5" width="21.6339285714286" customWidth="1"/>
     <col min="6" max="9" width="13.5" customWidth="1"/>
   </cols>
   <sheetData>
@@ -1191,8 +1179,8 @@
       </c>
       <c r="F1" s="1"/>
       <c r="G1" s="1"/>
-      <c r="H1" s="2"/>
-      <c r="I1" s="2"/>
+      <c r="H1" s="6"/>
+      <c r="I1" s="6"/>
     </row>
     <row r="2" spans="1:9">
       <c r="A2" s="1" t="s">
@@ -1225,8 +1213,8 @@
       </c>
       <c r="F3" s="1"/>
       <c r="G3" s="1"/>
-      <c r="H3" s="2"/>
-      <c r="I3" s="2"/>
+      <c r="H3" s="6"/>
+      <c r="I3" s="6"/>
     </row>
     <row r="4" spans="1:9">
       <c r="A4" s="1" t="s">
@@ -1242,188 +1230,188 @@
       <c r="I4" s="1"/>
     </row>
     <row r="5" spans="1:9">
-      <c r="A5" s="3" t="s">
+      <c r="A5" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="B5" s="3" t="s">
+      <c r="B5" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="C5" s="3"/>
-      <c r="D5" s="3"/>
-      <c r="E5" s="3"/>
-      <c r="F5" s="4"/>
-      <c r="G5" s="4"/>
-      <c r="H5" s="5"/>
-      <c r="I5" s="5"/>
-    </row>
-    <row r="6" ht="14.55" spans="2:9">
-      <c r="B6" s="6" t="s">
+      <c r="C5" s="2"/>
+      <c r="D5" s="2"/>
+      <c r="E5" s="2"/>
+      <c r="F5" s="7"/>
+      <c r="G5" s="7"/>
+      <c r="H5" s="8"/>
+      <c r="I5" s="8"/>
+    </row>
+    <row r="6" ht="17.55" spans="2:9">
+      <c r="B6" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="C6" s="6" t="s">
+      <c r="C6" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="D6" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="D6" s="6" t="s">
+      <c r="E6" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="E6" s="7" t="s">
+      <c r="F6" s="10"/>
+      <c r="G6" s="10"/>
+      <c r="H6" s="10"/>
+      <c r="I6" s="10"/>
+    </row>
+    <row r="7" ht="17.55" spans="2:9">
+      <c r="B7" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="F6" s="8"/>
-      <c r="G6" s="8"/>
-      <c r="H6" s="8"/>
-      <c r="I6" s="8"/>
-    </row>
-    <row r="7" ht="14.55" spans="2:9">
-      <c r="B7" s="6" t="s">
+      <c r="C7" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="D7" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="C7" s="6" t="s">
+      <c r="E7" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="F7" s="10"/>
+      <c r="G7" s="10"/>
+      <c r="H7" s="10"/>
+      <c r="I7" s="10"/>
+    </row>
+    <row r="8" ht="17.55" spans="2:9">
+      <c r="B8" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="D7" s="6" t="s">
+      <c r="C8" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="D8" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="E7" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="F7" s="8"/>
-      <c r="G7" s="8"/>
-      <c r="H7" s="8"/>
-      <c r="I7" s="8"/>
-    </row>
-    <row r="8" ht="14.55" spans="2:9">
-      <c r="B8" s="6" t="s">
+      <c r="E8" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="F8" s="5"/>
+      <c r="G8" s="5"/>
+      <c r="H8" s="5"/>
+      <c r="I8" s="5"/>
+    </row>
+    <row r="9" ht="17.55" spans="2:9">
+      <c r="B9" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="C8" s="6" t="s">
+      <c r="C9" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="D8" s="6" t="s">
+      <c r="D9" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="E8" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="F8" s="9"/>
-      <c r="G8" s="9"/>
-      <c r="H8" s="9"/>
-      <c r="I8" s="9"/>
-    </row>
-    <row r="9" ht="14.55" spans="2:9">
-      <c r="B9" s="6" t="s">
+      <c r="E9" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="F9" s="5"/>
+      <c r="G9" s="5"/>
+      <c r="H9" s="5"/>
+      <c r="I9" s="5"/>
+    </row>
+    <row r="10" ht="17.55" spans="2:9">
+      <c r="B10" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="C9" s="6" t="s">
+      <c r="C10" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="D10" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="D9" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="E9" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="F9" s="9"/>
-      <c r="G9" s="9"/>
-      <c r="H9" s="9"/>
-      <c r="I9" s="9"/>
-    </row>
-    <row r="10" ht="14.55" spans="2:9">
-      <c r="B10" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="C10" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="D10" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="E10" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="F10" s="9"/>
-      <c r="G10" s="9"/>
-      <c r="H10" s="9"/>
-      <c r="I10" s="9"/>
-    </row>
-    <row r="11" ht="14.55" spans="2:9">
-      <c r="B11" s="10"/>
-      <c r="C11" s="10"/>
-      <c r="D11" s="10"/>
-      <c r="E11" s="10"/>
-      <c r="F11" s="9"/>
-      <c r="G11" s="9"/>
-      <c r="H11" s="9"/>
-      <c r="I11" s="9"/>
-    </row>
-    <row r="12" ht="14.55" spans="2:9">
-      <c r="B12" s="10"/>
-      <c r="C12" s="10"/>
-      <c r="D12" s="10"/>
-      <c r="E12" s="10"/>
-      <c r="F12" s="9"/>
-      <c r="G12" s="9"/>
-      <c r="H12" s="9"/>
-      <c r="I12" s="9"/>
-    </row>
-    <row r="13" ht="14.55" spans="2:9">
-      <c r="B13" s="10"/>
-      <c r="C13" s="10"/>
-      <c r="D13" s="10"/>
-      <c r="E13" s="10"/>
-      <c r="F13" s="9"/>
-      <c r="G13" s="9"/>
-      <c r="H13" s="9"/>
-      <c r="I13" s="9"/>
-    </row>
-    <row r="14" ht="14.55" spans="2:9">
-      <c r="B14" s="10"/>
-      <c r="C14" s="10"/>
-      <c r="D14" s="10"/>
-      <c r="E14" s="10"/>
-      <c r="F14" s="9"/>
-      <c r="G14" s="9"/>
-      <c r="H14" s="9"/>
-      <c r="I14" s="9"/>
-    </row>
-    <row r="15" ht="14.55" spans="2:9">
-      <c r="B15" s="10"/>
-      <c r="C15" s="10"/>
-      <c r="D15" s="10"/>
-      <c r="E15" s="10"/>
-      <c r="F15" s="9"/>
-      <c r="G15" s="9"/>
-      <c r="H15" s="9"/>
-      <c r="I15" s="9"/>
-    </row>
-    <row r="16" ht="14.55" spans="2:9">
-      <c r="B16" s="10"/>
-      <c r="C16" s="10"/>
-      <c r="D16" s="10"/>
-      <c r="E16" s="10"/>
-      <c r="F16" s="9"/>
-      <c r="G16" s="9"/>
-      <c r="H16" s="9"/>
-      <c r="I16" s="9"/>
-    </row>
-    <row r="17" ht="14.55" spans="2:9">
-      <c r="B17" s="10"/>
-      <c r="C17" s="10"/>
-      <c r="D17" s="10"/>
-      <c r="E17" s="10"/>
-      <c r="F17" s="9"/>
-      <c r="G17" s="9"/>
-      <c r="H17" s="9"/>
-      <c r="I17" s="9"/>
-    </row>
-    <row r="18" ht="14.55" spans="2:2">
-      <c r="B18" s="9"/>
-    </row>
-    <row r="19" ht="14.55" spans="2:2">
-      <c r="B19" s="9"/>
-    </row>
-    <row r="20" ht="14.55" spans="2:2">
-      <c r="B20" s="9"/>
+      <c r="E10" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="F10" s="5"/>
+      <c r="G10" s="5"/>
+      <c r="H10" s="5"/>
+      <c r="I10" s="5"/>
+    </row>
+    <row r="11" ht="17.55" spans="2:9">
+      <c r="B11" s="4"/>
+      <c r="C11" s="4"/>
+      <c r="D11" s="4"/>
+      <c r="E11" s="4"/>
+      <c r="F11" s="5"/>
+      <c r="G11" s="5"/>
+      <c r="H11" s="5"/>
+      <c r="I11" s="5"/>
+    </row>
+    <row r="12" ht="17.55" spans="2:9">
+      <c r="B12" s="4"/>
+      <c r="C12" s="4"/>
+      <c r="D12" s="4"/>
+      <c r="E12" s="4"/>
+      <c r="F12" s="5"/>
+      <c r="G12" s="5"/>
+      <c r="H12" s="5"/>
+      <c r="I12" s="5"/>
+    </row>
+    <row r="13" ht="17.55" spans="2:9">
+      <c r="B13" s="4"/>
+      <c r="C13" s="4"/>
+      <c r="D13" s="4"/>
+      <c r="E13" s="4"/>
+      <c r="F13" s="5"/>
+      <c r="G13" s="5"/>
+      <c r="H13" s="5"/>
+      <c r="I13" s="5"/>
+    </row>
+    <row r="14" ht="17.55" spans="2:9">
+      <c r="B14" s="4"/>
+      <c r="C14" s="4"/>
+      <c r="D14" s="4"/>
+      <c r="E14" s="4"/>
+      <c r="F14" s="5"/>
+      <c r="G14" s="5"/>
+      <c r="H14" s="5"/>
+      <c r="I14" s="5"/>
+    </row>
+    <row r="15" ht="17.55" spans="2:9">
+      <c r="B15" s="4"/>
+      <c r="C15" s="4"/>
+      <c r="D15" s="4"/>
+      <c r="E15" s="4"/>
+      <c r="F15" s="5"/>
+      <c r="G15" s="5"/>
+      <c r="H15" s="5"/>
+      <c r="I15" s="5"/>
+    </row>
+    <row r="16" ht="17.55" spans="2:9">
+      <c r="B16" s="4"/>
+      <c r="C16" s="4"/>
+      <c r="D16" s="4"/>
+      <c r="E16" s="4"/>
+      <c r="F16" s="5"/>
+      <c r="G16" s="5"/>
+      <c r="H16" s="5"/>
+      <c r="I16" s="5"/>
+    </row>
+    <row r="17" ht="17.55" spans="2:9">
+      <c r="B17" s="4"/>
+      <c r="C17" s="4"/>
+      <c r="D17" s="4"/>
+      <c r="E17" s="4"/>
+      <c r="F17" s="5"/>
+      <c r="G17" s="5"/>
+      <c r="H17" s="5"/>
+      <c r="I17" s="5"/>
+    </row>
+    <row r="18" ht="17.55" spans="2:2">
+      <c r="B18" s="5"/>
+    </row>
+    <row r="19" ht="17.55" spans="2:2">
+      <c r="B19" s="5"/>
+    </row>
+    <row r="20" ht="17.55" spans="2:2">
+      <c r="B20" s="5"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
